--- a/data/trans_orig/IP2904-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47040</t>
+          <t>47659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61316</t>
+          <t>60719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>55072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89471</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111977</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35403</t>
+          <t>35202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54513</t>
+          <t>54788</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>35797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24174</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>39866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72721</t>
+          <t>71974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>36618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>60493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>69286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>36906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43669</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>62426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49966</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>31476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44419</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59858</t>
+          <t>59169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>24069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39484</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55571</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50842</t>
+          <t>50421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100746</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34640</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48704</t>
+          <t>48682</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70743</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>36494</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53674</t>
+          <t>54172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>86682</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>112224</t>
+          <t>112534</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87699</t>
+          <t>87375</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107486</t>
+          <t>107330</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>84202</t>
+          <t>83429</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>103980</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>178389</t>
+          <t>177946</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>205748</t>
+          <t>204813</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>42155</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>62843</t>
+          <t>63210</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22926</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>77398</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>278296</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>317608</t>
+          <t>317733</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>288736</t>
+          <t>289489</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>329705</t>
+          <t>331745</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>578445</t>
+          <t>578726</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>634669</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>164861</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>203473</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>306843</t>
+          <t>306527</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>354995</t>
+          <t>353938</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>187317</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>225634</t>
+          <t>225327</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>182447</t>
+          <t>183005</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>220578</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>381633</t>
+          <t>382393</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>433063</t>
+          <t>433687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37593</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34716</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59134</t>
+          <t>58867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>63283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50575</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>66806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102609</t>
+          <t>102460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>125141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26751</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44504</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>34905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45720</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21533</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53017</t>
+          <t>53488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>72183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94010</t>
+          <t>94642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36749</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42864</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62552</t>
+          <t>62997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34905</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>61949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29598</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51984</t>
+          <t>52791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51488</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70221</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58013</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96622</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>122242</t>
+          <t>123027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53625</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71773</t>
+          <t>69871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>117945</t>
+          <t>119204</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>37247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>38899</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71838</t>
+          <t>70821</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71185</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91709</t>
+          <t>92253</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>100686</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>155262</t>
+          <t>155223</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185377</t>
+          <t>184603</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>47526</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>61897</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>86926</t>
+          <t>87553</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>69079</t>
+          <t>67631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>93863</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>303964</t>
+          <t>307035</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>349135</t>
+          <t>350857</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>332471</t>
+          <t>333598</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>377113</t>
+          <t>378764</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>650897</t>
+          <t>654035</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>714500</t>
+          <t>716641</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>188361</t>
+          <t>187067</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>172078</t>
+          <t>171519</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>332316</t>
+          <t>332666</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>386578</t>
+          <t>386409</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>170323</t>
+          <t>168054</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>210176</t>
+          <t>207643</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>157398</t>
+          <t>155120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>195737</t>
+          <t>195794</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>336186</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>390196</t>
+          <t>388809</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61635</t>
+          <t>62301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38051</t>
+          <t>37815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>45207</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>64136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63582</t>
+          <t>63429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>65500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>100783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>123776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>40672</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60670</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39556</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53429</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37848</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>47658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65784</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27738</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>44001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74441</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>43425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63611</t>
+          <t>62572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84221</t>
+          <t>83105</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51839</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65227</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46229</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52105</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61968</t>
+          <t>61978</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>98888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>125881</t>
+          <t>125789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>47727</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>59543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76935</t>
+          <t>77280</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>103017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83392</t>
+          <t>82154</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>59505</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>77694</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61368</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>81746</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>125958</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>153441</t>
+          <t>153281</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>63474</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>40007</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58252</t>
+          <t>58112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>89314</t>
+          <t>88905</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>116172</t>
+          <t>115777</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>61668</t>
+          <t>61072</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>85771</t>
+          <t>85411</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>277523</t>
+          <t>275526</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>318552</t>
+          <t>315396</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>279414</t>
+          <t>277987</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>320163</t>
+          <t>324235</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>569025</t>
+          <t>565086</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>626839</t>
+          <t>628218</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>197553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>170184</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>208488</t>
+          <t>208137</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>342735</t>
+          <t>340659</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>396319</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>182029</t>
+          <t>183560</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>222075</t>
+          <t>221708</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>202377</t>
+          <t>200266</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242740</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>396580</t>
+          <t>394293</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>452493</t>
+          <t>453292</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
